--- a/рейтинг1.xlsx
+++ b/рейтинг1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milena/Desktop/практика день 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milena/Desktop/практика день 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BB93867-439C-CA47-A0E2-079172B993D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D097F832-4AF0-0C41-BA00-386023F3A27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{5AA2073E-ADFE-4244-BEB5-301E194BC916}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34200" windowHeight="20120" xr2:uid="{5AA2073E-ADFE-4244-BEB5-301E194BC916}"/>
   </bookViews>
   <sheets>
     <sheet name="Итоговый Рейтинг" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
   <si>
     <t>ФИО</t>
   </si>
@@ -238,12 +238,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -251,6 +245,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -592,38 +592,38 @@
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="3" width="12.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="23" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.6640625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>46077</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>46078</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>46079</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>46080</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>46081</v>
       </c>
     </row>
@@ -637,7 +637,9 @@
       <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
@@ -651,7 +653,9 @@
       <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
@@ -665,7 +669,9 @@
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
@@ -679,51 +685,55 @@
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>46077</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>46078</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>46079</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <v>46080</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>46081</v>
       </c>
     </row>
@@ -737,7 +747,9 @@
       <c r="D13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
@@ -751,7 +763,9 @@
       <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
@@ -765,7 +779,9 @@
       <c r="D15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
@@ -779,23 +795,27 @@
       <c r="D16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="D17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
